--- a/img/LawBench_评测结果_all.xlsx
+++ b/img/LawBench_评测结果_all.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="384">
   <si>
     <t>任务名称</t>
   </si>
@@ -22,6 +22,9 @@
     <t>Qwen3-8B</t>
   </si>
   <si>
+    <t>alpha_star_law_8B</t>
+  </si>
+  <si>
     <t>Qwen3.5-9B</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>43.91</t>
   </si>
   <si>
+    <t>46.93 (+6.9%)</t>
+  </si>
+  <si>
     <t>48.82 (+11.2%)</t>
   </si>
   <si>
@@ -106,6 +112,9 @@
     <t>62.60</t>
   </si>
   <si>
+    <t>64.20 (+2.6%)</t>
+  </si>
+  <si>
     <t>77.80 (+24.3%)</t>
   </si>
   <si>
@@ -142,6 +151,9 @@
     <t>80.14</t>
   </si>
   <si>
+    <t>77.74 (-3.0%)</t>
+  </si>
+  <si>
     <t>72.12 (-10.0%)</t>
   </si>
   <si>
@@ -175,6 +187,9 @@
     <t>43.20</t>
   </si>
   <si>
+    <t>39.60 (-8.3%)</t>
+  </si>
+  <si>
     <t>34.60 (-19.9%)</t>
   </si>
   <si>
@@ -211,6 +226,9 @@
     <t>46.01</t>
   </si>
   <si>
+    <t>44.69 (-2.9%)</t>
+  </si>
+  <si>
     <t>41.00 (-10.9%)</t>
   </si>
   <si>
@@ -247,6 +265,9 @@
     <t>52.19</t>
   </si>
   <si>
+    <t>50.50 (-3.2%)</t>
+  </si>
+  <si>
     <t>48.62 (-6.8%)</t>
   </si>
   <si>
@@ -283,6 +304,9 @@
     <t>35.60</t>
   </si>
   <si>
+    <t>33.80 (-5.1%)</t>
+  </si>
+  <si>
     <t>35.20 (-1.1%)</t>
   </si>
   <si>
@@ -322,6 +346,9 @@
     <t>38.40</t>
   </si>
   <si>
+    <t>49.00 (+27.6%)</t>
+  </si>
+  <si>
     <t>44.40 (+15.6%)</t>
   </si>
   <si>
@@ -355,6 +382,9 @@
     <t>68.59</t>
   </si>
   <si>
+    <t>68.44 (-0.2%)</t>
+  </si>
+  <si>
     <t>74.83 (+9.1%)</t>
   </si>
   <si>
@@ -391,6 +421,9 @@
     <t>49.00</t>
   </si>
   <si>
+    <t>49.00 (+0.0%)</t>
+  </si>
+  <si>
     <t>59.60 (+21.6%)</t>
   </si>
   <si>
@@ -427,6 +460,9 @@
     <t>77.82</t>
   </si>
   <si>
+    <t>70.60 (-9.3%)</t>
+  </si>
+  <si>
     <t>77.01 (-1.0%)</t>
   </si>
   <si>
@@ -463,6 +499,9 @@
     <t>34.40</t>
   </si>
   <si>
+    <t>26.65 (-22.5%)</t>
+  </si>
+  <si>
     <t>32.59 (-5.3%)</t>
   </si>
   <si>
@@ -496,6 +535,9 @@
     <t>51.20</t>
   </si>
   <si>
+    <t>58.80 (+14.8%)</t>
+  </si>
+  <si>
     <t>59.40 (+16.0%)</t>
   </si>
   <si>
@@ -535,6 +577,9 @@
     <t>75.23</t>
   </si>
   <si>
+    <t>80.20 (+6.6%)</t>
+  </si>
+  <si>
     <t>79.75 (+6.0%)</t>
   </si>
   <si>
@@ -571,6 +616,9 @@
     <t>64.60</t>
   </si>
   <si>
+    <t>70.20 (+8.7%)</t>
+  </si>
+  <si>
     <t>70.80 (+9.6%)</t>
   </si>
   <si>
@@ -607,6 +655,9 @@
     <t>64.00</t>
   </si>
   <si>
+    <t>75.93 (+18.6%)</t>
+  </si>
+  <si>
     <t>76.86 (+20.1%)</t>
   </si>
   <si>
@@ -643,6 +694,9 @@
     <t>48.20</t>
   </si>
   <si>
+    <t>59.40 (+23.2%)</t>
+  </si>
+  <si>
     <t>60.80 (+26.1%)</t>
   </si>
   <si>
@@ -682,6 +736,9 @@
     <t>75.19</t>
   </si>
   <si>
+    <t>68.70 (-8.6%)</t>
+  </si>
+  <si>
     <t>85.36 (+13.5%)</t>
   </si>
   <si>
@@ -754,6 +811,9 @@
     <t>61.62</t>
   </si>
   <si>
+    <t>63.32 (+2.8%)</t>
+  </si>
+  <si>
     <t>62.92 (+2.1%)</t>
   </si>
   <si>
@@ -790,6 +850,9 @@
     <t>46.80</t>
   </si>
   <si>
+    <t>49.20 (+5.1%)</t>
+  </si>
+  <si>
     <t>48.00 (+2.6%)</t>
   </si>
   <si>
@@ -826,6 +889,9 @@
     <t>38.46</t>
   </si>
   <si>
+    <t>48.28 (+25.5%)</t>
+  </si>
+  <si>
     <t>37.31 (-3.0%)</t>
   </si>
   <si>
@@ -862,6 +928,9 @@
     <t>11.31</t>
   </si>
   <si>
+    <t>18.59 (+64.4%)</t>
+  </si>
+  <si>
     <t>11.90 (+5.2%)</t>
   </si>
   <si>
@@ -901,6 +970,9 @@
     <t>36.66</t>
   </si>
   <si>
+    <t>46.29 (+26.3%)</t>
+  </si>
+  <si>
     <t>42.75 (+16.6%)</t>
   </si>
   <si>
@@ -937,6 +1009,9 @@
     <t>11.29</t>
   </si>
   <si>
+    <t>16.94 (+50.0%)</t>
+  </si>
+  <si>
     <t>12.70 (+12.5%)</t>
   </si>
   <si>
@@ -973,6 +1048,9 @@
     <t>53.40</t>
   </si>
   <si>
+    <t>56.00 (+4.9%)</t>
+  </si>
+  <si>
     <t>65.40 (+22.5%)</t>
   </si>
   <si>
@@ -1012,6 +1090,9 @@
     <t>82.89</t>
   </si>
   <si>
+    <t>84.40 (+1.8%)</t>
+  </si>
+  <si>
     <t>92.01 (+11.0%)</t>
   </si>
   <si>
@@ -1046,6 +1127,9 @@
   </si>
   <si>
     <t>53.00</t>
+  </si>
+  <si>
+    <t>60.20 (+13.6%)</t>
   </si>
   <si>
     <t>72.40 (+36.6%)</t>
@@ -1510,15 +1594,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="14" width="20" customWidth="1"/>
+    <col min="3" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1561,1299 +1645,1392 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="M3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>51</v>
+      <c r="M4" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="M5" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>124</v>
+        <v>133</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>158</v>
+        <v>170</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>199</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>194</v>
+        <v>206</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>209</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>195</v>
+        <v>210</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>201</v>
+        <v>215</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>217</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>208</v>
+        <v>224</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>225</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>220</v>
+        <v>237</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>238</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>223</v>
+        <v>240</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>233</v>
+        <v>251</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>252</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>239</v>
+        <v>255</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>257</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>244</v>
+        <v>262</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>250</v>
+        <v>267</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>257</v>
+        <v>276</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>264</v>
+        <v>280</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>289</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>271</v>
+        <v>291</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>274</v>
+        <v>294</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>280</v>
+        <v>299</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>301</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>281</v>
+        <v>302</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>303</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>288</v>
+        <v>306</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>310</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>290</v>
+        <v>311</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>293</v>
+        <v>314</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>316</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>298</v>
+        <v>319</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>305</v>
+        <v>326</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>306</v>
+        <v>329</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>330</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>311</v>
+        <v>333</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>335</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>314</v>
+        <v>336</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>338</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>316</v>
+        <v>339</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>340</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>317</v>
+        <v>341</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>342</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>330</v>
+        <v>355</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>356</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>343</v>
+        <v>369</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>355</v>
+        <v>382</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>
